--- a/source_data/Source_Data_3T_Fig4_5.xlsx
+++ b/source_data/Source_Data_3T_Fig4_5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Spatial\code\paper\revision\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zyeon\Desktop\Spatial 분석\paper\NC_final_revision\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C28494-6CFE-4112-BF84-645BAD311A9E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDD0459-B815-40A4-A69B-005A84298F83}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17610" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fig4d_on_off_retrieval" sheetId="2" r:id="rId1"/>
@@ -22,27 +22,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
   <si>
     <t>Subject_ID</t>
-  </si>
-  <si>
-    <t>AntHP_onMINUSoff</t>
-  </si>
-  <si>
-    <t>PostHP_onMINUSoff</t>
-  </si>
-  <si>
-    <t>NodeAttractionIndex</t>
-  </si>
-  <si>
-    <t>AvgDistanceError</t>
-  </si>
-  <si>
-    <t>AntHP_activation</t>
-  </si>
-  <si>
-    <t>PostHP_activation</t>
   </si>
   <si>
     <t>x_plotted_resid</t>
@@ -52,6 +34,12 @@
   </si>
   <si>
     <t>PostHP_y_resid</t>
+  </si>
+  <si>
+    <t>AntHP_on_off_diff</t>
+  </si>
+  <si>
+    <t>PostHP_on_off_diff</t>
   </si>
 </sst>
 </file>
@@ -413,10 +401,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -602,456 +590,248 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" customWidth="1"/>
-    <col min="2" max="2" width="18.26953125" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" customWidth="1"/>
-    <col min="6" max="8" width="14.08984375" customWidth="1"/>
+    <col min="2" max="4" width="14.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5.426333339380407E-2</v>
+        <v>-4.3380153210542755E-2</v>
       </c>
       <c r="C2">
-        <v>0.23308109940396218</v>
+        <v>-0.54177520306912941</v>
       </c>
       <c r="D2">
-        <v>-0.49623559086526536</v>
-      </c>
-      <c r="E2">
-        <v>-0.16600417107964546</v>
-      </c>
-      <c r="F2">
-        <v>-4.3380153210542755E-2</v>
-      </c>
-      <c r="G2">
-        <v>-0.54177520306912941</v>
-      </c>
-      <c r="H2">
         <v>-8.0910034674553016E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>-4.4049857700555139E-2</v>
+        <v>-0.14748222928146792</v>
       </c>
       <c r="C3">
-        <v>0.18894485838177769</v>
+        <v>-0.62300870831110267</v>
       </c>
       <c r="D3">
-        <v>-0.70954982282312984</v>
-      </c>
-      <c r="E3">
-        <v>-0.27912664998174563</v>
-      </c>
-      <c r="F3">
-        <v>-0.14748222928146792</v>
-      </c>
-      <c r="G3">
-        <v>-0.62300870831110267</v>
-      </c>
-      <c r="H3">
         <v>-0.31277959150089962</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.19833643931577405</v>
+        <v>0.10211505667950566</v>
       </c>
       <c r="C4">
-        <v>0.24392365781508951</v>
+        <v>0.78339071296509433</v>
       </c>
       <c r="D4">
-        <v>0.86137742445141363</v>
-      </c>
-      <c r="E4">
-        <v>-2.3726977265058134E-3</v>
-      </c>
-      <c r="F4">
-        <v>0.10211505667950566</v>
-      </c>
-      <c r="G4">
-        <v>0.78339071296509433</v>
-      </c>
-      <c r="H4">
         <v>0.11189297886247254</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.32970409666413736</v>
+        <v>0.22039186434843611</v>
       </c>
       <c r="C5">
-        <v>0.14411499017433407</v>
+        <v>0.59295107792487323</v>
       </c>
       <c r="D5">
-        <v>0.37225350979821714</v>
-      </c>
-      <c r="E5">
-        <v>0.62069081768852008</v>
-      </c>
-      <c r="F5">
-        <v>0.22039186434843611</v>
-      </c>
-      <c r="G5">
-        <v>0.59295107792487323</v>
-      </c>
-      <c r="H5">
         <v>0.46642461753940578</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.7977583631347827E-3</v>
+        <v>-0.1040920367857632</v>
       </c>
       <c r="C6">
-        <v>0.17020870464418322</v>
+        <v>-0.88000367558498893</v>
       </c>
       <c r="D6">
-        <v>-1.0226140144851616</v>
-      </c>
-      <c r="E6">
-        <v>-0.62457775453205799</v>
-      </c>
-      <c r="F6">
-        <v>-0.1040920367857632</v>
-      </c>
-      <c r="G6">
-        <v>-0.88000367558498893</v>
-      </c>
-      <c r="H6">
         <v>-0.70863969002875737</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>-7.5906670293247269E-2</v>
+        <v>-0.18716288383747043</v>
       </c>
       <c r="C7">
-        <v>0.12929347888295897</v>
+        <v>-1.613710616855184</v>
       </c>
       <c r="D7">
-        <v>-1.8787625735082356</v>
-      </c>
-      <c r="E7">
-        <v>-1.2063236498797458E-3</v>
-      </c>
-      <c r="F7">
-        <v>-0.18716288383747043</v>
-      </c>
-      <c r="G7">
-        <v>-1.613710616855184</v>
-      </c>
-      <c r="H7">
         <v>-0.19534930341389981</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>7.5740985987983622E-2</v>
+        <v>-1.6961360624008909E-2</v>
       </c>
       <c r="C8">
-        <v>0.27075387170980847</v>
+        <v>-8.5289829680088344E-2</v>
       </c>
       <c r="D8">
-        <v>7.298813604729916E-2</v>
-      </c>
-      <c r="E8">
-        <v>-0.45355104291889198</v>
-      </c>
-      <c r="F8">
-        <v>-1.6961360624008909E-2</v>
-      </c>
-      <c r="G8">
-        <v>-8.5289829680088344E-2</v>
-      </c>
-      <c r="H8">
         <v>-0.26709957464731465</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.27807551263115737</v>
+        <v>0.17536478264054434</v>
       </c>
       <c r="C9">
-        <v>0.19444687600521227</v>
+        <v>0.51965427029859601</v>
       </c>
       <c r="D9">
-        <v>0.44957832067774317</v>
-      </c>
-      <c r="E9">
-        <v>0.54608595003282623</v>
-      </c>
-      <c r="F9">
-        <v>0.17536478264054434</v>
-      </c>
-      <c r="G9">
-        <v>0.51965427029859601</v>
-      </c>
-      <c r="H9">
         <v>0.52723600261419312</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.49703949700845707</v>
+        <v>0.38429398221962435</v>
       </c>
       <c r="C10">
-        <v>0.11793858775058765</v>
+        <v>0.76563832788629838</v>
       </c>
       <c r="D10">
-        <v>0.46660608116301638</v>
-      </c>
-      <c r="E10">
-        <v>5.0574855647139677E-2</v>
-      </c>
-      <c r="F10">
-        <v>0.38429398221962435</v>
-      </c>
-      <c r="G10">
-        <v>0.76563832788629838</v>
-      </c>
-      <c r="H10">
         <v>-0.17411807832433765</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>-0.2393873783911622</v>
+        <v>-0.35198431574974864</v>
       </c>
       <c r="C11">
-        <v>0.11907138781456401</v>
+        <v>0.6994686501166445</v>
       </c>
       <c r="D11">
-        <v>0.40382638523614339</v>
-      </c>
-      <c r="E11">
-        <v>0.75664821263036919</v>
-      </c>
-      <c r="F11">
-        <v>-0.35198431574974864</v>
-      </c>
-      <c r="G11">
-        <v>0.6994686501166445</v>
-      </c>
-      <c r="H11">
         <v>0.53500303928268356</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.14849553083392464</v>
+        <v>5.003113389025178E-2</v>
       </c>
       <c r="C12">
-        <v>0.2268222262805942</v>
+        <v>2.4465626577504861E-2</v>
       </c>
       <c r="D12">
-        <v>5.1275131925610971E-2</v>
-      </c>
-      <c r="E12">
-        <v>-0.15039907391441781</v>
-      </c>
-      <c r="F12">
-        <v>5.003113389025178E-2</v>
-      </c>
-      <c r="G12">
-        <v>2.4465626577504861E-2</v>
-      </c>
-      <c r="H12">
         <v>-8.2144225978068752E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.29045258810374341</v>
+        <v>0.18230572033695772</v>
       </c>
       <c r="C13">
-        <v>0.15300008822307068</v>
+        <v>0.49625205478291923</v>
       </c>
       <c r="D13">
-        <v>0.3021437516240072</v>
-      </c>
-      <c r="E13">
-        <v>-6.1324422629350762E-2</v>
-      </c>
-      <c r="F13">
-        <v>0.18230572033695772</v>
-      </c>
-      <c r="G13">
-        <v>0.49625205478291923</v>
-      </c>
-      <c r="H13">
         <v>-0.19168556412547341</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>-1.7480849218702854E-3</v>
+        <v>-0.10842807930585945</v>
       </c>
       <c r="C14">
-        <v>0.16418398243313334</v>
+        <v>-0.15161614562379699</v>
       </c>
       <c r="D14">
-        <v>-0.31225587872400734</v>
-      </c>
-      <c r="E14">
-        <v>0.24109756070494773</v>
-      </c>
-      <c r="F14">
-        <v>-0.10842807930585945</v>
-      </c>
-      <c r="G14">
-        <v>-0.15161614562379699</v>
-      </c>
-      <c r="H14">
         <v>0.14082631192513748</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1.8533527928099813E-2</v>
+        <v>-8.1905345297373838E-2</v>
       </c>
       <c r="C15">
-        <v>0.21176821131589504</v>
+        <v>-7.8913607967584884E-2</v>
       </c>
       <c r="D15">
-        <v>-9.7154274325989817E-2</v>
-      </c>
-      <c r="E15">
-        <v>-1.0805821543950848E-2</v>
-      </c>
-      <c r="F15">
-        <v>-8.1905345297373838E-2</v>
-      </c>
-      <c r="G15">
-        <v>-7.8913607967584884E-2</v>
-      </c>
-      <c r="H15">
         <v>1.6946703433191573E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>3.2565695479575441E-2</v>
+        <v>-7.0345868158598612E-2</v>
       </c>
       <c r="C16">
-        <v>0.19291565845468239</v>
+        <v>0.23853776326129458</v>
       </c>
       <c r="D16">
-        <v>0.16387954015837389</v>
-      </c>
-      <c r="E16">
-        <v>0.55219828630132339</v>
-      </c>
-      <c r="F16">
-        <v>-7.0345868158598612E-2</v>
-      </c>
-      <c r="G16">
-        <v>0.23853776326129458</v>
-      </c>
-      <c r="H16">
         <v>0.52922864935814851</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.11508168010086828</v>
+        <v>-2.7602678644870482E-3</v>
       </c>
       <c r="C17">
-        <v>7.908181240558923E-2</v>
+        <v>-0.14604069672134523</v>
       </c>
       <c r="D17">
-        <v>-0.56135450722401359</v>
-      </c>
-      <c r="E17">
-        <v>1.4403546029253951E-2</v>
-      </c>
-      <c r="F17">
-        <v>-2.7602678644870482E-3</v>
-      </c>
-      <c r="G17">
-        <v>-0.14604069672134523</v>
-      </c>
-      <c r="H17">
         <v>-0.31483224032193169</v>
       </c>
     </row>
@@ -1062,457 +842,249 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" customWidth="1"/>
-    <col min="2" max="2" width="15.26953125" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" customWidth="1"/>
-    <col min="4" max="4" width="16.08984375" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" customWidth="1"/>
-    <col min="6" max="6" width="15.08984375" customWidth="1"/>
-    <col min="7" max="8" width="14.08984375" customWidth="1"/>
+    <col min="2" max="2" width="15.08984375" customWidth="1"/>
+    <col min="3" max="4" width="14.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.23308109940396218</v>
+        <v>5.5049142278197238E-2</v>
       </c>
       <c r="C2">
-        <v>5.426333339380407E-2</v>
+        <v>-0.22882322857442378</v>
       </c>
       <c r="D2">
-        <v>-0.20976324400984914</v>
-      </c>
-      <c r="E2">
-        <v>-0.3444320048671215</v>
-      </c>
-      <c r="F2">
-        <v>5.5049142278197238E-2</v>
-      </c>
-      <c r="G2">
-        <v>-0.22882322857442378</v>
-      </c>
-      <c r="H2">
         <v>-0.58218082765261325</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.18894485838177769</v>
+        <v>9.826214466331612E-3</v>
       </c>
       <c r="C3">
-        <v>-4.4049857700555139E-2</v>
+        <v>0.95268440402528165</v>
       </c>
       <c r="D3">
-        <v>0.8977462712712293</v>
-      </c>
-      <c r="E3">
-        <v>0.84128386444221703</v>
-      </c>
-      <c r="F3">
-        <v>9.826214466331612E-3</v>
-      </c>
-      <c r="G3">
-        <v>0.95268440402528165</v>
-      </c>
-      <c r="H3">
         <v>0.57780519724550028</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.24392365781508951</v>
+        <v>6.7484186287757292E-2</v>
       </c>
       <c r="C4">
-        <v>0.19833643931577405</v>
+        <v>-0.2543632647230572</v>
       </c>
       <c r="D4">
-        <v>-0.12686270900216101</v>
-      </c>
-      <c r="E4">
-        <v>-6.2548977983268778E-2</v>
-      </c>
-      <c r="F4">
-        <v>6.7484186287757292E-2</v>
-      </c>
-      <c r="G4">
-        <v>-0.2543632647230572</v>
-      </c>
-      <c r="H4">
         <v>-0.26259198979924031</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.14411499017433407</v>
+        <v>-3.0872433095355811E-2</v>
       </c>
       <c r="C5">
-        <v>0.32970409666413736</v>
+        <v>-0.63424076100365467</v>
       </c>
       <c r="D5">
-        <v>-0.40786273815825658</v>
-      </c>
-      <c r="E5">
-        <v>0.59825515355030934</v>
-      </c>
-      <c r="F5">
-        <v>-3.0872433095355811E-2</v>
-      </c>
-      <c r="G5">
-        <v>-0.63424076100365467</v>
-      </c>
-      <c r="H5">
         <v>0.43259277109460731</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.17020870464418322</v>
+        <v>-8.4031710730160247E-3</v>
       </c>
       <c r="C6">
-        <v>1.7977583631347827E-3</v>
+        <v>-1.758938935783638</v>
       </c>
       <c r="D6">
-        <v>-1.7793686039614149</v>
-      </c>
-      <c r="E6">
-        <v>-0.43045159352914192</v>
-      </c>
-      <c r="F6">
-        <v>-8.4031710730160247E-3</v>
-      </c>
-      <c r="G6">
-        <v>-1.758938935783638</v>
-      </c>
-      <c r="H6">
         <v>-0.68193134161019175</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.12929347888295897</v>
+        <v>-5.0177288455808794E-2</v>
       </c>
       <c r="C7">
-        <v>-7.5906670293247269E-2</v>
+        <v>-0.28039260767434437</v>
       </c>
       <c r="D7">
-        <v>-0.35930864338720725</v>
-      </c>
-      <c r="E7">
-        <v>0.65452118336348741</v>
-      </c>
-      <c r="F7">
-        <v>-5.0177288455808794E-2</v>
-      </c>
-      <c r="G7">
-        <v>-0.28039260767434437</v>
-      </c>
-      <c r="H7">
         <v>0.38270517280192329</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.27075387170980847</v>
+        <v>9.2959313869812349E-2</v>
       </c>
       <c r="C8">
-        <v>7.5740985987983622E-2</v>
+        <v>0.18959624899647373</v>
       </c>
       <c r="D8">
-        <v>0.22482197733054338</v>
-      </c>
-      <c r="E8">
-        <v>-0.56255644837161578</v>
-      </c>
-      <c r="F8">
-        <v>9.2959313869812349E-2</v>
-      </c>
-      <c r="G8">
-        <v>0.18959624899647373</v>
-      </c>
-      <c r="H8">
         <v>-0.79468428933955892</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.19444687600521227</v>
+        <v>1.8888785670258146E-2</v>
       </c>
       <c r="C9">
-        <v>0.27807551263115737</v>
+        <v>0.69006842409340341</v>
       </c>
       <c r="D9">
-        <v>0.8775867784066278</v>
-      </c>
-      <c r="E9">
-        <v>0.49749639070089319</v>
-      </c>
-      <c r="F9">
-        <v>1.8888785670258146E-2</v>
-      </c>
-      <c r="G9">
-        <v>0.69006842409340341</v>
-      </c>
-      <c r="H9">
         <v>0.31832213441062646</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.11793858775058765</v>
+        <v>-5.5199224424435964E-2</v>
       </c>
       <c r="C10">
-        <v>0.49703949700845707</v>
+        <v>0.1990508186481269</v>
       </c>
       <c r="D10">
-        <v>0.55137841599521997</v>
-      </c>
-      <c r="E10">
-        <v>3.9471889669701977E-2</v>
-      </c>
-      <c r="F10">
-        <v>-5.5199224424435964E-2</v>
-      </c>
-      <c r="G10">
-        <v>0.1990508186481269</v>
-      </c>
-      <c r="H10">
         <v>-8.239663595536334E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.11907138781456401</v>
+        <v>-6.2206383486542935E-2</v>
       </c>
       <c r="C11">
-        <v>-0.2393873783911622</v>
+        <v>0.81041159637975602</v>
       </c>
       <c r="D11">
-        <v>0.60844732591321726</v>
-      </c>
-      <c r="E11">
-        <v>0.73664866125292938</v>
-      </c>
-      <c r="F11">
-        <v>-6.2206383486542935E-2</v>
-      </c>
-      <c r="G11">
-        <v>0.81041159637975602</v>
-      </c>
-      <c r="H11">
         <v>0.42204761709847649</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.2268222262805942</v>
+        <v>4.9831847431161647E-2</v>
       </c>
       <c r="C12">
-        <v>0.14849553083392464</v>
+        <v>-9.0753809561832946E-2</v>
       </c>
       <c r="D12">
-        <v>-7.673793825137545E-4</v>
-      </c>
-      <c r="E12">
-        <v>-2.3212717199284208E-2</v>
-      </c>
-      <c r="F12">
-        <v>4.9831847431161647E-2</v>
-      </c>
-      <c r="G12">
-        <v>-9.0753809561832946E-2</v>
-      </c>
-      <c r="H12">
         <v>-0.236299744841385</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.15300008822307068</v>
+        <v>-2.2421194382816478E-2</v>
       </c>
       <c r="C13">
-        <v>0.29045258810374341</v>
+        <v>0.72334487111182566</v>
       </c>
       <c r="D13">
-        <v>0.92017917044409514</v>
-      </c>
-      <c r="E13">
-        <v>0.58465937973037152</v>
-      </c>
-      <c r="F13">
-        <v>-2.2421194382816478E-2</v>
-      </c>
-      <c r="G13">
-        <v>0.72334487111182566</v>
-      </c>
-      <c r="H13">
         <v>0.40872436552583846</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.16418398243313334</v>
+        <v>-1.4467086611158669E-2</v>
       </c>
       <c r="C14">
-        <v>-1.7480849218702854E-3</v>
+        <v>-5.2447292248425779E-2</v>
       </c>
       <c r="D14">
-        <v>-7.5545836540145878E-2</v>
-      </c>
-      <c r="E14">
-        <v>0.51522421016404729</v>
-      </c>
-      <c r="F14">
-        <v>-1.4467086611158669E-2</v>
-      </c>
-      <c r="G14">
-        <v>-5.2447292248425779E-2</v>
-      </c>
-      <c r="H14">
         <v>0.26281646864677377</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.21176821131589504</v>
+        <v>3.334132135186843E-2</v>
       </c>
       <c r="C15">
-        <v>1.8533527928099813E-2</v>
+        <v>-5.5781316828624299E-2</v>
       </c>
       <c r="D15">
-        <v>-6.3614349438980936E-2</v>
-      </c>
-      <c r="E15">
-        <v>-0.26675065128686087</v>
-      </c>
-      <c r="F15">
-        <v>3.334132135186843E-2</v>
-      </c>
-      <c r="G15">
-        <v>-5.5781316828624299E-2</v>
-      </c>
-      <c r="H15">
         <v>-0.51385043018762677</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.19291565845468239</v>
+        <v>1.4643870475842535E-2</v>
       </c>
       <c r="C16">
-        <v>3.2565695479575441E-2</v>
+        <v>-0.15824895612262341</v>
       </c>
       <c r="D16">
-        <v>-0.15552029330685832</v>
-      </c>
-      <c r="E16">
-        <v>0.28419842924700972</v>
-      </c>
-      <c r="F16">
-        <v>1.4643870475842535E-2</v>
-      </c>
-      <c r="G16">
-        <v>-0.15824895612262341</v>
-      </c>
-      <c r="H16">
         <v>4.0771051616437431E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>7.908181240558923E-2</v>
+        <v>-9.8277900302095739E-2</v>
       </c>
       <c r="C17">
-        <v>0.11508168010086828</v>
+        <v>-5.1166190734242528E-2</v>
       </c>
       <c r="D17">
-        <v>1.3670389062957825E-2</v>
-      </c>
-      <c r="E17">
-        <v>0.52998234914256936</v>
-      </c>
-      <c r="F17">
-        <v>-9.8277900302095739E-2</v>
-      </c>
-      <c r="G17">
-        <v>-5.1166190734242528E-2</v>
-      </c>
-      <c r="H17">
         <v>0.30815048094579389</v>
       </c>
     </row>

--- a/source_data/Source_Data_3T_Fig4_5.xlsx
+++ b/source_data/Source_Data_3T_Fig4_5.xlsx
@@ -5,41 +5,44 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zyeon\Desktop\Spatial 분석\paper\NC_final_revision\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Spatial\code\paper\KIM_code_availability_NC\source_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDD0459-B815-40A4-A69B-005A84298F83}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE884EB-11D9-49EF-A6B5-DE6C3F3DA8E9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17610" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fig4d_on_off_retrieval" sheetId="2" r:id="rId1"/>
-    <sheet name="Fig4f_corr_encoding" sheetId="3" r:id="rId2"/>
-    <sheet name="Fig5a_corr_retrieval" sheetId="4" r:id="rId3"/>
+    <sheet name="Fig4f_corr" sheetId="3" r:id="rId2"/>
+    <sheet name="Fig5a_corr" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
   <si>
     <t>Subject_ID</t>
-  </si>
-  <si>
-    <t>x_plotted_resid</t>
-  </si>
-  <si>
-    <t>AntHP_y_resid</t>
-  </si>
-  <si>
-    <t>PostHP_y_resid</t>
   </si>
   <si>
     <t>AntHP_on_off_diff</t>
   </si>
   <si>
     <t>PostHP_on_off_diff</t>
+  </si>
+  <si>
+    <t>node_attraction_idx_resid</t>
+  </si>
+  <si>
+    <t>AvgDistErr_resid</t>
+  </si>
+  <si>
+    <t>HP_Ant_activation_resid</t>
+  </si>
+  <si>
+    <t>HP_Post_activation_resid</t>
   </si>
 </sst>
 </file>
@@ -401,10 +404,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -594,7 +597,9 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" customWidth="1"/>
-    <col min="2" max="4" width="14.08984375" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -602,13 +607,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -846,8 +851,9 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" customWidth="1"/>
-    <col min="3" max="4" width="14.08984375" customWidth="1"/>
+    <col min="2" max="2" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -855,13 +861,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
